--- a/data/FCF_Futsal_BCN_Gr10_2025_26_DB.xlsx
+++ b/data/FCF_Futsal_BCN_Gr10_2025_26_DB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a6a8126cde9cbf5/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{4ECBE5C0-2CF3-4542-B65B-0E288D5FFD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B70B88D2-36B7-4FB9-969A-CEC19CE38553}"/>
+  <xr:revisionPtr revIDLastSave="452" documentId="13_ncr:1_{4ECBE5C0-2CF3-4542-B65B-0E288D5FFD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27D3A459-5523-432D-9440-5D375513B2FA}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matches" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="25">
   <si>
     <t>MatchID</t>
   </si>
@@ -197,10 +197,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -490,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="10.19921875" bestFit="1" customWidth="1"/>
@@ -544,6 +540,12 @@
       <c r="F2" t="s">
         <v>17</v>
       </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3">
@@ -564,6 +566,12 @@
       <c r="F3" t="s">
         <v>18</v>
       </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4">
@@ -609,6 +617,12 @@
       </c>
       <c r="F5" t="s">
         <v>20</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
@@ -630,6 +644,12 @@
       <c r="F6" t="s">
         <v>21</v>
       </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7">
@@ -650,6 +670,12 @@
       <c r="F7" t="s">
         <v>22</v>
       </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8">
@@ -670,6 +696,12 @@
       <c r="F8" t="s">
         <v>23</v>
       </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9">
@@ -689,6 +721,12 @@
       </c>
       <c r="F9" t="s">
         <v>24</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
@@ -918,6 +956,12 @@
       <c r="F18" t="s">
         <v>18</v>
       </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>4</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19">
@@ -1723,6 +1767,1854 @@
       </c>
       <c r="H49">
         <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50">
+        <v>7</v>
+      </c>
+      <c r="D50" s="3">
+        <v>45976</v>
+      </c>
+      <c r="E50" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50">
+        <v>4</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51">
+        <v>7</v>
+      </c>
+      <c r="D51" s="3">
+        <v>45976</v>
+      </c>
+      <c r="E51" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52">
+        <v>7</v>
+      </c>
+      <c r="D52" s="3">
+        <v>45976</v>
+      </c>
+      <c r="E52" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" t="s">
+        <v>22</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53">
+        <v>7</v>
+      </c>
+      <c r="D53" s="3">
+        <v>45976</v>
+      </c>
+      <c r="E53" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" t="s">
+        <v>23</v>
+      </c>
+      <c r="G53">
+        <v>2</v>
+      </c>
+      <c r="H53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54">
+        <v>7</v>
+      </c>
+      <c r="D54" s="3">
+        <v>45976</v>
+      </c>
+      <c r="E54" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" t="s">
+        <v>24</v>
+      </c>
+      <c r="G54">
+        <v>6</v>
+      </c>
+      <c r="H54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55">
+        <v>7</v>
+      </c>
+      <c r="D55" s="3">
+        <v>45976</v>
+      </c>
+      <c r="E55" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55">
+        <v>4</v>
+      </c>
+      <c r="H55">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56">
+        <v>7</v>
+      </c>
+      <c r="D56" s="3">
+        <v>45976</v>
+      </c>
+      <c r="E56" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56">
+        <v>4</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57">
+        <v>7</v>
+      </c>
+      <c r="D57" s="3">
+        <v>45976</v>
+      </c>
+      <c r="E57" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57">
+        <v>2</v>
+      </c>
+      <c r="H57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58">
+        <v>8</v>
+      </c>
+      <c r="D58" s="3">
+        <v>45983</v>
+      </c>
+      <c r="E58" t="s">
+        <v>20</v>
+      </c>
+      <c r="F58" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58">
+        <v>4</v>
+      </c>
+      <c r="H58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59">
+        <v>8</v>
+      </c>
+      <c r="D59" s="3">
+        <v>45983</v>
+      </c>
+      <c r="E59" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59">
+        <v>4</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60">
+        <v>8</v>
+      </c>
+      <c r="D60" s="3">
+        <v>45983</v>
+      </c>
+      <c r="E60" t="s">
+        <v>22</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60">
+        <v>5</v>
+      </c>
+      <c r="H60">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61">
+        <v>8</v>
+      </c>
+      <c r="D61" s="3">
+        <v>45983</v>
+      </c>
+      <c r="E61" t="s">
+        <v>23</v>
+      </c>
+      <c r="F61" t="s">
+        <v>17</v>
+      </c>
+      <c r="G61">
+        <v>2</v>
+      </c>
+      <c r="H61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62">
+        <v>8</v>
+      </c>
+      <c r="D62" s="3">
+        <v>45983</v>
+      </c>
+      <c r="E62" t="s">
+        <v>24</v>
+      </c>
+      <c r="F62" t="s">
+        <v>9</v>
+      </c>
+      <c r="G62">
+        <v>4</v>
+      </c>
+      <c r="H62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63">
+        <v>8</v>
+      </c>
+      <c r="D63" s="3">
+        <v>45983</v>
+      </c>
+      <c r="E63" t="s">
+        <v>15</v>
+      </c>
+      <c r="F63" t="s">
+        <v>10</v>
+      </c>
+      <c r="G63">
+        <v>5</v>
+      </c>
+      <c r="H63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64">
+        <v>8</v>
+      </c>
+      <c r="D64" s="3">
+        <v>45983</v>
+      </c>
+      <c r="E64" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" t="s">
+        <v>11</v>
+      </c>
+      <c r="G64">
+        <v>2</v>
+      </c>
+      <c r="H64">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65">
+        <v>8</v>
+      </c>
+      <c r="D65" s="3">
+        <v>45983</v>
+      </c>
+      <c r="E65" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" t="s">
+        <v>12</v>
+      </c>
+      <c r="G65">
+        <v>2</v>
+      </c>
+      <c r="H65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66">
+        <v>9</v>
+      </c>
+      <c r="D66" s="3">
+        <v>45990</v>
+      </c>
+      <c r="E66" t="s">
+        <v>20</v>
+      </c>
+      <c r="F66" t="s">
+        <v>21</v>
+      </c>
+      <c r="G66">
+        <v>2</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67">
+        <v>9</v>
+      </c>
+      <c r="D67" s="3">
+        <v>45990</v>
+      </c>
+      <c r="E67" t="s">
+        <v>19</v>
+      </c>
+      <c r="F67" t="s">
+        <v>22</v>
+      </c>
+      <c r="G67">
+        <v>3</v>
+      </c>
+      <c r="H67">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68">
+        <v>9</v>
+      </c>
+      <c r="D68" s="3">
+        <v>45990</v>
+      </c>
+      <c r="E68" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" t="s">
+        <v>23</v>
+      </c>
+      <c r="G68">
+        <v>3</v>
+      </c>
+      <c r="H68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69">
+        <v>9</v>
+      </c>
+      <c r="D69" s="3">
+        <v>45990</v>
+      </c>
+      <c r="E69" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69" t="s">
+        <v>24</v>
+      </c>
+      <c r="G69">
+        <v>2</v>
+      </c>
+      <c r="H69">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70">
+        <v>9</v>
+      </c>
+      <c r="D70" s="3">
+        <v>45990</v>
+      </c>
+      <c r="E70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" t="s">
+        <v>15</v>
+      </c>
+      <c r="G70">
+        <v>5</v>
+      </c>
+      <c r="H70">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71">
+        <v>9</v>
+      </c>
+      <c r="D71" s="3">
+        <v>45990</v>
+      </c>
+      <c r="E71" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71">
+        <v>9</v>
+      </c>
+      <c r="H71">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72">
+        <v>9</v>
+      </c>
+      <c r="D72" s="3">
+        <v>45990</v>
+      </c>
+      <c r="E72" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" t="s">
+        <v>11</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73">
+        <v>9</v>
+      </c>
+      <c r="D73" s="3">
+        <v>45990</v>
+      </c>
+      <c r="E73" t="s">
+        <v>16</v>
+      </c>
+      <c r="F73" t="s">
+        <v>12</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74">
+        <v>10</v>
+      </c>
+      <c r="D74" s="3">
+        <v>46004</v>
+      </c>
+      <c r="E74" t="s">
+        <v>21</v>
+      </c>
+      <c r="F74" t="s">
+        <v>16</v>
+      </c>
+      <c r="G74">
+        <v>8</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75">
+        <v>10</v>
+      </c>
+      <c r="D75" s="3">
+        <v>46004</v>
+      </c>
+      <c r="E75" t="s">
+        <v>22</v>
+      </c>
+      <c r="F75" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75">
+        <v>4</v>
+      </c>
+      <c r="H75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76">
+        <v>10</v>
+      </c>
+      <c r="D76" s="3">
+        <v>46004</v>
+      </c>
+      <c r="E76" t="s">
+        <v>23</v>
+      </c>
+      <c r="F76" t="s">
+        <v>19</v>
+      </c>
+      <c r="G76">
+        <v>6</v>
+      </c>
+      <c r="H76">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77">
+        <v>10</v>
+      </c>
+      <c r="D77" s="3">
+        <v>46004</v>
+      </c>
+      <c r="E77" t="s">
+        <v>24</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78">
+        <v>10</v>
+      </c>
+      <c r="D78" s="3">
+        <v>46004</v>
+      </c>
+      <c r="E78" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" t="s">
+        <v>17</v>
+      </c>
+      <c r="G78">
+        <v>6</v>
+      </c>
+      <c r="H78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79">
+        <v>10</v>
+      </c>
+      <c r="D79" s="3">
+        <v>46004</v>
+      </c>
+      <c r="E79" t="s">
+        <v>14</v>
+      </c>
+      <c r="F79" t="s">
+        <v>9</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="H79">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80">
+        <v>10</v>
+      </c>
+      <c r="D80" s="3">
+        <v>46004</v>
+      </c>
+      <c r="E80" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" t="s">
+        <v>10</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81">
+        <v>10</v>
+      </c>
+      <c r="D81" s="3">
+        <v>46004</v>
+      </c>
+      <c r="E81" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" t="s">
+        <v>11</v>
+      </c>
+      <c r="G81">
+        <v>2</v>
+      </c>
+      <c r="H81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82">
+        <v>11</v>
+      </c>
+      <c r="D82" s="3">
+        <v>46011</v>
+      </c>
+      <c r="E82" t="s">
+        <v>21</v>
+      </c>
+      <c r="F82" t="s">
+        <v>22</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83">
+        <v>11</v>
+      </c>
+      <c r="D83" s="3">
+        <v>46011</v>
+      </c>
+      <c r="E83" t="s">
+        <v>20</v>
+      </c>
+      <c r="F83" t="s">
+        <v>23</v>
+      </c>
+      <c r="G83">
+        <v>2</v>
+      </c>
+      <c r="H83">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84">
+        <v>11</v>
+      </c>
+      <c r="D84" s="3">
+        <v>46011</v>
+      </c>
+      <c r="E84" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" t="s">
+        <v>24</v>
+      </c>
+      <c r="G84">
+        <v>2</v>
+      </c>
+      <c r="H84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85">
+        <v>11</v>
+      </c>
+      <c r="D85" s="3">
+        <v>46011</v>
+      </c>
+      <c r="E85" t="s">
+        <v>18</v>
+      </c>
+      <c r="F85" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86">
+        <v>11</v>
+      </c>
+      <c r="D86" s="3">
+        <v>46011</v>
+      </c>
+      <c r="E86" t="s">
+        <v>17</v>
+      </c>
+      <c r="F86" t="s">
+        <v>14</v>
+      </c>
+      <c r="G86">
+        <v>3</v>
+      </c>
+      <c r="H86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87">
+        <v>11</v>
+      </c>
+      <c r="D87" s="3">
+        <v>46011</v>
+      </c>
+      <c r="E87" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88">
+        <v>11</v>
+      </c>
+      <c r="D88" s="3">
+        <v>46011</v>
+      </c>
+      <c r="E88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" t="s">
+        <v>12</v>
+      </c>
+      <c r="G88">
+        <v>4</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89">
+        <v>11</v>
+      </c>
+      <c r="D89" s="3">
+        <v>46011</v>
+      </c>
+      <c r="E89" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90">
+        <v>12</v>
+      </c>
+      <c r="D90" s="3">
+        <v>46032</v>
+      </c>
+      <c r="E90" t="s">
+        <v>22</v>
+      </c>
+      <c r="F90" t="s">
+        <v>16</v>
+      </c>
+      <c r="G90">
+        <v>8</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91">
+        <v>12</v>
+      </c>
+      <c r="D91" s="3">
+        <v>46032</v>
+      </c>
+      <c r="E91" t="s">
+        <v>23</v>
+      </c>
+      <c r="F91" t="s">
+        <v>21</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92">
+        <v>12</v>
+      </c>
+      <c r="D92" s="3">
+        <v>46032</v>
+      </c>
+      <c r="E92" t="s">
+        <v>24</v>
+      </c>
+      <c r="F92" t="s">
+        <v>20</v>
+      </c>
+      <c r="G92">
+        <v>5</v>
+      </c>
+      <c r="H92">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93">
+        <v>12</v>
+      </c>
+      <c r="D93" s="3">
+        <v>46032</v>
+      </c>
+      <c r="E93" t="s">
+        <v>15</v>
+      </c>
+      <c r="F93" t="s">
+        <v>19</v>
+      </c>
+      <c r="G93">
+        <v>6</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94">
+        <v>12</v>
+      </c>
+      <c r="D94" s="3">
+        <v>46032</v>
+      </c>
+      <c r="E94" t="s">
+        <v>14</v>
+      </c>
+      <c r="F94" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95">
+        <v>12</v>
+      </c>
+      <c r="D95" s="3">
+        <v>46032</v>
+      </c>
+      <c r="E95" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" t="s">
+        <v>17</v>
+      </c>
+      <c r="G95">
+        <v>4</v>
+      </c>
+      <c r="H95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>8</v>
+      </c>
+      <c r="C96">
+        <v>12</v>
+      </c>
+      <c r="D96" s="3">
+        <v>46032</v>
+      </c>
+      <c r="E96" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" t="s">
+        <v>9</v>
+      </c>
+      <c r="G96">
+        <v>2</v>
+      </c>
+      <c r="H96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>8</v>
+      </c>
+      <c r="C97">
+        <v>12</v>
+      </c>
+      <c r="D97" s="3">
+        <v>46032</v>
+      </c>
+      <c r="E97" t="s">
+        <v>11</v>
+      </c>
+      <c r="F97" t="s">
+        <v>10</v>
+      </c>
+      <c r="G97">
+        <v>2</v>
+      </c>
+      <c r="H97">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98">
+        <v>13</v>
+      </c>
+      <c r="D98" s="3">
+        <v>46039</v>
+      </c>
+      <c r="E98" t="s">
+        <v>22</v>
+      </c>
+      <c r="F98" t="s">
+        <v>23</v>
+      </c>
+      <c r="G98">
+        <v>2</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99">
+        <v>13</v>
+      </c>
+      <c r="D99" s="3">
+        <v>46039</v>
+      </c>
+      <c r="E99" t="s">
+        <v>21</v>
+      </c>
+      <c r="F99" t="s">
+        <v>24</v>
+      </c>
+      <c r="G99">
+        <v>4</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>8</v>
+      </c>
+      <c r="C100">
+        <v>13</v>
+      </c>
+      <c r="D100" s="3">
+        <v>46039</v>
+      </c>
+      <c r="E100" t="s">
+        <v>20</v>
+      </c>
+      <c r="F100" t="s">
+        <v>15</v>
+      </c>
+      <c r="G100">
+        <v>2</v>
+      </c>
+      <c r="H100">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>8</v>
+      </c>
+      <c r="C101">
+        <v>13</v>
+      </c>
+      <c r="D101" s="3">
+        <v>46039</v>
+      </c>
+      <c r="E101" t="s">
+        <v>19</v>
+      </c>
+      <c r="F101" t="s">
+        <v>14</v>
+      </c>
+      <c r="G101">
+        <v>9</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>8</v>
+      </c>
+      <c r="C102">
+        <v>13</v>
+      </c>
+      <c r="D102" s="3">
+        <v>46039</v>
+      </c>
+      <c r="E102" t="s">
+        <v>18</v>
+      </c>
+      <c r="F102" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102">
+        <v>2</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>8</v>
+      </c>
+      <c r="C103">
+        <v>13</v>
+      </c>
+      <c r="D103" s="3">
+        <v>46039</v>
+      </c>
+      <c r="E103" t="s">
+        <v>17</v>
+      </c>
+      <c r="F103" t="s">
+        <v>12</v>
+      </c>
+      <c r="G103">
+        <v>5</v>
+      </c>
+      <c r="H103">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104">
+        <v>13</v>
+      </c>
+      <c r="D104" s="3">
+        <v>46039</v>
+      </c>
+      <c r="E104" t="s">
+        <v>9</v>
+      </c>
+      <c r="F104" t="s">
+        <v>11</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>8</v>
+      </c>
+      <c r="C105">
+        <v>13</v>
+      </c>
+      <c r="D105" s="3">
+        <v>46039</v>
+      </c>
+      <c r="E105" t="s">
+        <v>16</v>
+      </c>
+      <c r="F105" t="s">
+        <v>10</v>
+      </c>
+      <c r="G105">
+        <v>2</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>8</v>
+      </c>
+      <c r="C106">
+        <v>14</v>
+      </c>
+      <c r="D106" s="3">
+        <v>46046</v>
+      </c>
+      <c r="E106" t="s">
+        <v>16</v>
+      </c>
+      <c r="F106" t="s">
+        <v>23</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+      <c r="H106">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>8</v>
+      </c>
+      <c r="C107">
+        <v>14</v>
+      </c>
+      <c r="D107" s="3">
+        <v>46046</v>
+      </c>
+      <c r="E107" t="s">
+        <v>24</v>
+      </c>
+      <c r="F107" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>8</v>
+      </c>
+      <c r="C108">
+        <v>14</v>
+      </c>
+      <c r="D108" s="3">
+        <v>46046</v>
+      </c>
+      <c r="E108" t="s">
+        <v>15</v>
+      </c>
+      <c r="F108" t="s">
+        <v>21</v>
+      </c>
+      <c r="G108">
+        <v>2</v>
+      </c>
+      <c r="H108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109">
+        <v>14</v>
+      </c>
+      <c r="D109" s="3">
+        <v>46046</v>
+      </c>
+      <c r="E109" t="s">
+        <v>14</v>
+      </c>
+      <c r="F109" t="s">
+        <v>20</v>
+      </c>
+      <c r="G109">
+        <v>3</v>
+      </c>
+      <c r="H109">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>8</v>
+      </c>
+      <c r="C110">
+        <v>14</v>
+      </c>
+      <c r="D110" s="3">
+        <v>46046</v>
+      </c>
+      <c r="E110" t="s">
+        <v>13</v>
+      </c>
+      <c r="F110" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>8</v>
+      </c>
+      <c r="C111">
+        <v>14</v>
+      </c>
+      <c r="D111" s="3">
+        <v>46046</v>
+      </c>
+      <c r="E111" t="s">
+        <v>12</v>
+      </c>
+      <c r="F111" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>8</v>
+      </c>
+      <c r="C112">
+        <v>14</v>
+      </c>
+      <c r="D112" s="3">
+        <v>46046</v>
+      </c>
+      <c r="E112" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" t="s">
+        <v>17</v>
+      </c>
+      <c r="G112">
+        <v>5</v>
+      </c>
+      <c r="H112">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>8</v>
+      </c>
+      <c r="C113">
+        <v>14</v>
+      </c>
+      <c r="D113" s="3">
+        <v>46046</v>
+      </c>
+      <c r="E113" t="s">
+        <v>10</v>
+      </c>
+      <c r="F113" t="s">
+        <v>9</v>
+      </c>
+      <c r="G113">
+        <v>3</v>
+      </c>
+      <c r="H113">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>8</v>
+      </c>
+      <c r="C114">
+        <v>15</v>
+      </c>
+      <c r="D114" s="3">
+        <v>46053</v>
+      </c>
+      <c r="E114" t="s">
+        <v>23</v>
+      </c>
+      <c r="F114" t="s">
+        <v>24</v>
+      </c>
+      <c r="G114">
+        <v>6</v>
+      </c>
+      <c r="H114">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>8</v>
+      </c>
+      <c r="C115">
+        <v>15</v>
+      </c>
+      <c r="D115" s="3">
+        <v>46053</v>
+      </c>
+      <c r="E115" t="s">
+        <v>22</v>
+      </c>
+      <c r="F115" t="s">
+        <v>15</v>
+      </c>
+      <c r="G115">
+        <v>2</v>
+      </c>
+      <c r="H115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>8</v>
+      </c>
+      <c r="C116">
+        <v>15</v>
+      </c>
+      <c r="D116" s="3">
+        <v>46053</v>
+      </c>
+      <c r="E116" t="s">
+        <v>21</v>
+      </c>
+      <c r="F116" t="s">
+        <v>14</v>
+      </c>
+      <c r="G116">
+        <v>3</v>
+      </c>
+      <c r="H116">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>8</v>
+      </c>
+      <c r="C117">
+        <v>15</v>
+      </c>
+      <c r="D117" s="3">
+        <v>46053</v>
+      </c>
+      <c r="E117" t="s">
+        <v>20</v>
+      </c>
+      <c r="F117" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117">
+        <v>3</v>
+      </c>
+      <c r="H117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>8</v>
+      </c>
+      <c r="C118">
+        <v>15</v>
+      </c>
+      <c r="D118" s="3">
+        <v>46053</v>
+      </c>
+      <c r="E118" t="s">
+        <v>19</v>
+      </c>
+      <c r="F118" t="s">
+        <v>12</v>
+      </c>
+      <c r="G118">
+        <v>5</v>
+      </c>
+      <c r="H118">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>8</v>
+      </c>
+      <c r="C119">
+        <v>15</v>
+      </c>
+      <c r="D119" s="3">
+        <v>46053</v>
+      </c>
+      <c r="E119" t="s">
+        <v>18</v>
+      </c>
+      <c r="F119" t="s">
+        <v>11</v>
+      </c>
+      <c r="G119">
+        <v>2</v>
+      </c>
+      <c r="H119">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>8</v>
+      </c>
+      <c r="C120">
+        <v>15</v>
+      </c>
+      <c r="D120" s="3">
+        <v>46053</v>
+      </c>
+      <c r="E120" t="s">
+        <v>17</v>
+      </c>
+      <c r="F120" t="s">
+        <v>10</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
+      <c r="H120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>8</v>
+      </c>
+      <c r="C121">
+        <v>15</v>
+      </c>
+      <c r="D121" s="3">
+        <v>46053</v>
+      </c>
+      <c r="E121" t="s">
+        <v>9</v>
+      </c>
+      <c r="F121" t="s">
+        <v>16</v>
+      </c>
+      <c r="G121">
+        <v>2</v>
+      </c>
+      <c r="H121">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
